--- a/F3M_Transaccional_assessment_ready_AI.xlsx
+++ b/F3M_Transaccional_assessment_ready_AI.xlsx
@@ -135,7 +135,7 @@
     <t>Planificación predictiva de gasto y demanda de terceros basada en contratos, históricos y señales externas, con recomendaciones de sourcing y timing.</t>
   </si>
   <si>
-    <t>Using data from contract management system, forecast monthly expense for all third-party contracts; Resilient logistics and planning</t>
+    <t>Previsión del gasto mensual de todos los contratos con terceros con datos del sistema de gestión de contratos; Logística y planificación resilientes</t>
   </si>
   <si>
     <t>¿Existe planificación de demanda de compras?
@@ -168,10 +168,10 @@
     <t>Gestión integrada de desempeño, riesgos, cumplimiento y oportunidades de mejora por proveedor.</t>
   </si>
   <si>
-    <t>Motor AI de evaluación de proveedores, riesgo supply chain y recomendaciones de selección/negociación basadas en desempeño, riesgo y contexto externo.</t>
-  </si>
-  <si>
-    <t>Resilient logistics and planning; Supplier assessment AI; Drafting contracts and SoWs</t>
+    <t>Motor IA de evaluación de proveedores, riesgo supply chain y recomendaciones de selección/negociación basadas en desempeño, riesgo y contexto externo.</t>
+  </si>
+  <si>
+    <t>Logística y planificación resilientes; IA de evaluación de proveedores; Redacción de contratos y SoW</t>
   </si>
   <si>
     <t>¿Hay criterios de homologación?
@@ -204,10 +204,10 @@
     <t>Gestión contractual integrada con compras, legal, presupuesto y proveedores, con alertas y trazabilidad de cambios.</t>
   </si>
   <si>
-    <t>Asistente AI para generar RFPs, contratos y SoWs, extraer cláusulas, analizar riesgos y recomendar condiciones financieras/comerciales.</t>
-  </si>
-  <si>
-    <t>Drafting contracts and SoWs; AI-powered RFP and knowledge assistant; Using data from contract management system forecast monthly expense</t>
+    <t>Asistente IA para generar RFPs, contratos y SoWs, extraer cláusulas, analizar riesgos y recomendar condiciones financieras/comerciales.</t>
+  </si>
+  <si>
+    <t>Redacción de contratos y SoW; Asistente de RFP y de conocimiento impulsado por IA; Previsión del gasto mensual con datos del sistema de gestión de contratos</t>
   </si>
   <si>
     <t>¿Existe repositorio contractual?
@@ -219,7 +219,7 @@
     <t>Contratos; RFPs; SoWs; repositorio; workflow de aprobación; matriz de cláusulas; contratos vencidos.</t>
   </si>
   <si>
-    <t>Implantar asistente contractual AI para generación, revisión y explotación financiera de contratos y SoWs.</t>
+    <t>Implantar asistente contractual IA para generación, revisión y explotación financiera de contratos y SoWs.</t>
   </si>
   <si>
     <t>1.4 Orden de compra, recepción y aprobación</t>
@@ -240,10 +240,10 @@
     <t>Workflow integrado con catálogo, recepción, presupuesto, contrato y controles automáticos.</t>
   </si>
   <si>
-    <t>AI recomienda timing óptimo de pagos/compras, detecta excepciones operativas y prioriza aprobaciones según impacto en caja, contrato y riesgo.</t>
-  </si>
-  <si>
-    <t>Recommend most optimal payment timing; Proactive defect resolution recommendations; Guided adaptable workflows for master data record changes</t>
+    <t>IA recomienda timing óptimo de pagos/compras, detecta excepciones operativas y prioriza aprobaciones según impacto en caja, contrato y riesgo.</t>
+  </si>
+  <si>
+    <t>Recomendación del momento óptimo de pago; Recomendaciones proactivas para la resolución de incidencias; Flujos guiados y adaptables para cambios en datos maestros</t>
   </si>
   <si>
     <t>¿Qué % de compras tiene PO?
@@ -279,10 +279,10 @@
     <t>Pedidos integrados con contratos, pricing, crédito, facturación y controles automáticos.</t>
   </si>
   <si>
-    <t>Asistente AI analiza contratos/pedidos, valida obligaciones y condiciones comerciales, y recomienda acciones para evitar errores, revenue leakage o disputas.</t>
-  </si>
-  <si>
-    <t>Read customer contracts and identify performance obligations; Identify &amp; proactively correct revenue leakage; AI assistant for vehicle buying and leasing</t>
+    <t>Asistente IA analiza contratos/pedidos, valida obligaciones y condiciones comerciales, y recomienda acciones para evitar errores, revenue leakage o disputas.</t>
+  </si>
+  <si>
+    <t>Lectura de contratos de cliente e identificación de obligaciones de desempeño; Identificación y corrección proactiva de fugas de ingresos; Asistente de IA para la compra y el leasing de vehículos</t>
   </si>
   <si>
     <t>¿Qué validaciones existen sobre pedidos?
@@ -315,10 +315,10 @@
     <t>Facturación integrada con pedidos, contratos, impuestos, entregas y controles automáticos de error.</t>
   </si>
   <si>
-    <t>Detección/corrección AI de errores de factura y generación de facturas personalizadas para pedidos no estándar, con validación fiscal/contable.</t>
-  </si>
-  <si>
-    <t>Automated invoice error detection &amp; correction; Generate customized invoices for nonstandard customer orders</t>
+    <t>Detección/corrección IA de errores de factura y generación de facturas personalizadas para pedidos no estándar, con validación fiscal/contable.</t>
+  </si>
+  <si>
+    <t>Detección y corrección automatizada de errores en facturas; Generación de facturas personalizadas para pedidos de cliente no estándar</t>
   </si>
   <si>
     <t>¿Qué errores de factura son recurrentes?
@@ -330,7 +330,7 @@
     <t>Facturas; notas de crédito; errores; controles; logs de emisión; KPI first-time-right.</t>
   </si>
   <si>
-    <t>Implantar motor AI de validación y corrección preventiva de facturas antes de emisión.</t>
+    <t>Implantar motor IA de validación y corrección preventiva de facturas antes de emisión.</t>
   </si>
   <si>
     <t>2.3 Cobros, aplicación de pagos y gestión de disputas</t>
@@ -351,10 +351,10 @@
     <t>Cash application automatizada, segmentación de cartera, workflow de disputas y control de aging/DSO.</t>
   </si>
   <si>
-    <t>Asistente AI identifica gaps de cobro, automatiza outreach, recomienda payment terms para mejorar DSO y apoya recuperación de ingresos/disputas.</t>
-  </si>
-  <si>
-    <t>Facilitate payment collection to identify collections gaps and automate outreach; Recommend optimal payment terms to improve DSO; Denial appeal letters</t>
+    <t>Asistente IA identifica gaps de cobro, automatiza outreach, recomienda payment terms para mejorar DSO y apoya recuperación de ingresos/disputas.</t>
+  </si>
+  <si>
+    <t>Facilitación del cobro para identificar brechas de recobro y automatizar el contacto; Recomendación de condiciones de pago óptimas para mejorar el DSO; Cartas de recurso ante denegaciones</t>
   </si>
   <si>
     <t>¿Cómo se aplican cobros?
@@ -387,10 +387,10 @@
     <t>Riesgo cliente integrado con pedidos, cobros, aging, límites y alertas de exposición.</t>
   </si>
   <si>
-    <t>Scoring dinámico AI de cliente y riesgo de cobro, con alertas tempranas, recomendaciones de bloqueo/liberación y condiciones comerciales.</t>
-  </si>
-  <si>
-    <t>AI agents for credit underwriting; Predicts late payments or defaults; Recommend optimal payment terms to improve DSO</t>
+    <t>Scoring dinámico IA de cliente y riesgo de cobro, con alertas tempranas, recomendaciones de bloqueo/liberación y condiciones comerciales.</t>
+  </si>
+  <si>
+    <t>Agentes de IA para el análisis de riesgo crediticio; Predicción de retrasos en el pago o impagos; Recomendación de condiciones de pago óptimas para mejorar el DSO</t>
   </si>
   <si>
     <t>¿Existen límites de crédito?
@@ -426,10 +426,10 @@
     <t>Proceso integrado con compras, proyectos, contabilidad y control presupuestario.</t>
   </si>
   <si>
-    <t>AI ayuda a clasificar gastos vs activos, detectar errores de codificación y generar metadata/documentación de activos.</t>
-  </si>
-  <si>
-    <t>Identify expense classification errors; Generate metadata documentation; Guided adaptable workflows for master data record changes</t>
+    <t>IA ayuda a clasificar gastos vs activos, detectar errores de codificación y generar metadata/documentación de activos.</t>
+  </si>
+  <si>
+    <t>Identificación de errores de clasificación de gastos; Generación de documentación de metadatos; Flujos guiados y adaptables para cambios en datos maestros</t>
   </si>
   <si>
     <t>¿Están claras las políticas CAPEX/OPEX?
@@ -461,10 +461,10 @@
     <t>Trazabilidad integrada de altas, bajas, traslados, mantenimiento, ubicación y estado de activos.</t>
   </si>
   <si>
-    <t>AI/digital sensing permite detectar inconsistencias, anomalías de activos y generar alertas sobre activos críticos o no conciliados.</t>
-  </si>
-  <si>
-    <t>Identify inconsistencies in master data records; AI-powered archive access and extraction; Autonomous drone-based infrastructure inspection</t>
+    <t>IA/digital sensing permite detectar inconsistencias, anomalías de activos y generar alertas sobre activos críticos o no conciliados.</t>
+  </si>
+  <si>
+    <t>Identificación de inconsistencias en los registros de datos maestros; Acceso y extracción documental impulsados por IA; Inspección autónoma de infraestructuras con drones</t>
   </si>
   <si>
     <t>¿Existe inventario actualizado?
@@ -497,10 +497,10 @@
     <t>Modelo integrado con reporting, planificación de activos, KPIs operativos y revisiones estructuradas.</t>
   </si>
   <si>
-    <t>Modelos AI detectan patrones de deterioro, anomalías de uso/coste y recomiendan revisión de vida útil, impairment o mantenimiento.</t>
-  </si>
-  <si>
-    <t>AI-driven predictive maintenance; Identify past data patterns to predict and improve future financial performance</t>
+    <t>Modelos IA detectan patrones de deterioro, anomalías de uso/coste y recomiendan revisión de vida útil, impairment o mantenimiento.</t>
+  </si>
+  <si>
+    <t>Mantenimiento predictivo basado en IA; Identificación de patrones históricos para predecir y mejorar el rendimiento financiero futuro</t>
   </si>
   <si>
     <t>¿Se revisan vidas útiles?
@@ -532,10 +532,10 @@
     <t>Control integrado de CAPEX, activos, proyectos, aprobaciones, beneficios y desviaciones.</t>
   </si>
   <si>
-    <t>AI prioriza decisiones de inversión/desinversión mediante business case, coste evitado, riesgo de activo y escenarios de rendimiento.</t>
-  </si>
-  <si>
-    <t>Project-level recommendations; AI-driven predictive maintenance; Autonomous drone-based infrastructure inspection</t>
+    <t>IA prioriza decisiones de inversión/desinversión mediante business case, coste evitado, riesgo de activo y escenarios de rendimiento.</t>
+  </si>
+  <si>
+    <t>Recomendaciones a nivel de proyecto; Mantenimiento predictivo basado en IA; Inspección autónoma de infraestructuras con drones</t>
   </si>
   <si>
     <t>¿Cómo se aprueban bajas?
@@ -571,10 +571,10 @@
     <t>KPIs integrados, automatizados y conectados con procesos, productividad, coste y control.</t>
   </si>
   <si>
-    <t>AI genera alertas e insights operativos en tiempo real, detecta desviaciones y recomienda acciones de mejora.</t>
-  </si>
-  <si>
-    <t>Proactive defect resolution recommendations; Next-generation store operations; AI agents for service lifecycle management</t>
+    <t>IA genera alertas e insights operativos en tiempo real, detecta desviaciones y recomienda acciones de mejora.</t>
+  </si>
+  <si>
+    <t>Recomendaciones proactivas para la resolución de incidencias; Operaciones de tienda de nueva generación; Agentes de IA para la gestión del ciclo de vida del servicio</t>
   </si>
   <si>
     <t>¿Existe catálogo de KPIs?
@@ -607,10 +607,10 @@
     <t>Capa integrada de datos operativos-financieros, controles automáticos y gestión de incidencias.</t>
   </si>
   <si>
-    <t>AI detecta inconsistencias en master data, automatiza datos de fuentes diversas y guía workflows de cambios de datos maestros.</t>
-  </si>
-  <si>
-    <t>Guided adaptable workflows for master data record changes; Identify inconsistencies in master data records; Automate financial data across diverse sources</t>
+    <t>IA detecta inconsistencias en master data, automatiza datos de fuentes diversas y guía workflows de cambios de datos maestros.</t>
+  </si>
+  <si>
+    <t>Flujos guiados y adaptables para cambios en datos maestros; Identificación de inconsistencias en los registros de datos maestros; Automatización de datos financieros de fuentes diversas</t>
   </si>
   <si>
     <t>¿Qué fuentes alimentan reporting?
@@ -643,10 +643,10 @@
     <t>Reporting automatizado, con drill-down, alertas, comentarios y acceso por rol.</t>
   </si>
   <si>
-    <t>AI permite reporting operativo bajo demanda, búsqueda conversacional, extracción histórica y generación de resúmenes ejecutivos.</t>
-  </si>
-  <si>
-    <t>Data access for all; Enterprise-wide data search and access; AI-powered archive access and extraction</t>
+    <t>IA permite reporting operativo bajo demanda, búsqueda conversacional, extracción histórica y generación de resúmenes ejecutivos.</t>
+  </si>
+  <si>
+    <t>Acceso a datos para toda la organización; Búsqueda y acceso a datos en toda la compañía; Acceso y extracción documental impulsados por IA</t>
   </si>
   <si>
     <t>¿Cuánto esfuerzo manual requiere el reporting?
@@ -679,10 +679,10 @@
     <t>Modelo de mejora continua basado en KPIs, root cause, priorización e impacto financiero.</t>
   </si>
   <si>
-    <t>AI prioriza incidencias, recomienda resolución, asigna tareas y aprende de tiempos reales de ejecución para mejorar productividad.</t>
-  </si>
-  <si>
-    <t>Proactive defect resolution recommendations; Autonomous field operations management; AI-driven permitting</t>
+    <t>IA prioriza incidencias, recomienda resolución, asigna tareas y aprende de tiempos reales de ejecución para mejorar productividad.</t>
+  </si>
+  <si>
+    <t>Recomendaciones proactivas para la resolución de incidencias; Gestión autónoma de operaciones de campo; Gestión de permisos basada en IA</t>
   </si>
   <si>
     <t>¿Se asignan acciones?
@@ -694,7 +694,7 @@
     <t>Trackers de acciones; incidencias; actas; KPIs; planes de mejora; análisis causa-raíz.</t>
   </si>
   <si>
-    <t>Implantar workflow de gestión de incidencias con priorización AI, root cause y seguimiento de beneficios.</t>
+    <t>Implantar workflow de gestión de incidencias con priorización IA, root cause y seguimiento de beneficios.</t>
   </si>
   <si>
     <t>Contabilidad de proyectos</t>
@@ -718,10 +718,10 @@
     <t>Alta integrada con business case, presupuesto, compras, tiempos, facturación y reporting.</t>
   </si>
   <si>
-    <t>AI asiste la creación de estructuras de proyecto, clasificación de costes, metadata y documentación a partir de contratos, SoWs y planes.</t>
-  </si>
-  <si>
-    <t>Drafting contracts and SoWs; Generate metadata documentation; AI-powered RFP and knowledge assistant</t>
+    <t>IA asiste la creación de estructuras de proyecto, clasificación de costes, metadata y documentación a partir de contratos, SoWs y planes.</t>
+  </si>
+  <si>
+    <t>Redacción de contratos y SoW; Generación de documentación de metadatos; Asistente de RFP y de conocimiento impulsado por IA</t>
   </si>
   <si>
     <t>¿Existe codificación estándar?
@@ -754,10 +754,10 @@
     <t>Control integrado de costes reales, comprometidos, forecast, presupuesto y margen por proyecto.</t>
   </si>
   <si>
-    <t>AI detecta errores de clasificación/imputación, anomalías de coste y recomienda acciones para corregir desviaciones tempranamente.</t>
-  </si>
-  <si>
-    <t>Identify expense classification errors; Proactive defect resolution recommendations; Identify past data patterns to predict and improve future financial performance</t>
+    <t>IA detecta errores de clasificación/imputación, anomalías de coste y recomienda acciones para corregir desviaciones tempranamente.</t>
+  </si>
+  <si>
+    <t>Identificación de errores de clasificación de gastos; Recomendaciones proactivas para la resolución de incidencias; Identificación de patrones históricos para predecir y mejorar el rendimiento financiero futuro</t>
   </si>
   <si>
     <t>¿Se imputan costes correctamente?
@@ -790,10 +790,10 @@
     <t>Integración entre contrato, avance, costes, facturación, ingresos y margen, con controles preventivos.</t>
   </si>
   <si>
-    <t>AI identifica obligaciones contractuales, genera alertas de hitos/facturación y detecta revenue leakage o riesgo de margen.</t>
-  </si>
-  <si>
-    <t>Read customer contracts and identify performance obligations; Identify &amp; proactively correct revenue leakage; Automated invoice error detection &amp; correction</t>
+    <t>IA identifica obligaciones contractuales, genera alertas de hitos/facturación y detecta revenue leakage o riesgo de margen.</t>
+  </si>
+  <si>
+    <t>Lectura de contratos de cliente e identificación de obligaciones de desempeño; Identificación y corrección proactiva de fugas de ingresos; Detección y corrección automatizada de errores en facturas</t>
   </si>
   <si>
     <t>¿Los hitos disparan facturación?
@@ -805,7 +805,7 @@
     <t>Contrato; hitos; facturas; ingresos; margen; avance; notas de crédito; revenue recognition.</t>
   </si>
   <si>
-    <t>Crear control AI de contrato-hito-factura-ingreso-margen para proyectos, con alertas de leakage y desviaciones.</t>
+    <t>Crear control IA de contrato-hito-factura-ingreso-margen para proyectos, con alertas de leakage y desviaciones.</t>
   </si>
   <si>
     <t>5.4 Forecast, cierre y análisis del proyecto</t>
@@ -826,10 +826,10 @@
     <t>Forecast integrado coste-ingreso-caja, revisión de margen, lecciones aprendidas y acciones de mejora.</t>
   </si>
   <si>
-    <t>AI predice performance futura del proyecto, genera escenarios, recomendaciones y resumen ejecutivo de salud financiera.</t>
-  </si>
-  <si>
-    <t>Identify past data patterns to predict and improve future financial performance; Generate executive level overview of company financial health; Project-level recommendations</t>
+    <t>IA predice performance futura del proyecto, genera escenarios, recomendaciones y resumen ejecutivo de salud financiera.</t>
+  </si>
+  <si>
+    <t>Identificación de patrones históricos para predecir y mejorar el rendimiento financiero futuro; Generación de una visión ejecutiva de la salud financiera de la compañía; Recomendaciones a nivel de proyecto</t>
   </si>
   <si>
     <t>¿Se actualiza forecast de proyectos?

--- a/F3M_Transaccional_assessment_ready_AI.xlsx
+++ b/F3M_Transaccional_assessment_ready_AI.xlsx
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="316">
   <si>
     <t>Capacidad</t>
   </si>
@@ -995,6 +995,66 @@
   </si>
   <si>
     <t>Assessment, Resumen, Heatmap, Roadmap, AI Overlay, Guias scoring e Instrucciones.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Previsión del gasto contratado con terceros; Planificación logística resiliente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planificación logística resiliente; Evaluación de proveedores con IA; Redacción de contratos y pliegos; Insights sobre el dato de proveedor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Redacción de contratos y pliegos; Asistente de RFP y de conocimiento comercial; Previsión del gasto contratado con terceros</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Momento óptimo de pago a proveedores; Recomendaciones de resolución de incidencias; Flujos guiados de cambio en datos maestros; Detección de facturas duplicadas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lectura de contratos y obligaciones de desempeño; Detección de fugas de ingresos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Detección y corrección de errores en facturas; Facturación de pedidos no estándar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gestión asistida del recobro; Condiciones de pago óptimas para el DSO; Redacción de recursos ante denegaciones; Asistente financiero para el cliente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agentes de IA para análisis de riesgo crediticio; Predicción de retraso e impago; Condiciones de pago óptimas para el DSO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Detección de errores de clasificación de gasto; Generación de documentación de metadatos; Flujos guiados de cambio en datos maestros</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Detección de inconsistencias en datos maestros; Acceso y extracción documental</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mantenimiento predictivo de activos; Patrones históricos para predecir el rendimiento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recomendaciones de acción a nivel de proyecto; Mantenimiento predictivo de activos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recomendaciones de resolución de incidencias; Análisis de desviaciones con explicación automática</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flujos guiados de cambio en datos maestros; Detección de inconsistencias en datos maestros; Integración automatizada de datos financieros</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consulta del dato en lenguaje natural; Acceso y extracción documental</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recomendaciones de resolución de incidencias; Predicción de retraso e impago</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Redacción de contratos y pliegos; Generación de documentación de metadatos; Asistente de RFP y de conocimiento comercial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Detección de errores de clasificación de gasto; Recomendaciones de resolución de incidencias; Patrones históricos para predecir el rendimiento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lectura de contratos y obligaciones de desempeño; Detección de fugas de ingresos; Detección y corrección de errores en facturas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patrones históricos para predecir el rendimiento; Visión ejecutiva de la salud financiera; Recomendaciones de acción a nivel de proyecto</t>
   </si>
 </sst>
 </file>
@@ -1745,7 +1805,7 @@
         <v>27</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>28</v>
+        <v>296</v>
       </c>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
@@ -1803,7 +1863,7 @@
         <v>38</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>39</v>
+        <v>297</v>
       </c>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
@@ -1861,7 +1921,7 @@
         <v>49</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>50</v>
+        <v>298</v>
       </c>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
@@ -1919,7 +1979,7 @@
         <v>60</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>61</v>
+        <v>299</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -1977,7 +2037,7 @@
         <v>72</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>73</v>
+        <v>300</v>
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
@@ -2035,7 +2095,7 @@
         <v>83</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>84</v>
+        <v>301</v>
       </c>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
@@ -2093,7 +2153,7 @@
         <v>94</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>95</v>
+        <v>302</v>
       </c>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
@@ -2151,7 +2211,7 @@
         <v>105</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>106</v>
+        <v>303</v>
       </c>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
@@ -2209,7 +2269,7 @@
         <v>117</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>118</v>
+        <v>304</v>
       </c>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
@@ -2267,7 +2327,7 @@
         <v>128</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>129</v>
+        <v>305</v>
       </c>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
@@ -2325,7 +2385,7 @@
         <v>139</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>140</v>
+        <v>306</v>
       </c>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
@@ -2383,7 +2443,7 @@
         <v>150</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>151</v>
+        <v>307</v>
       </c>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
@@ -2441,7 +2501,7 @@
         <v>162</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>163</v>
+        <v>308</v>
       </c>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
@@ -2499,7 +2559,7 @@
         <v>173</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>174</v>
+        <v>309</v>
       </c>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
@@ -2557,7 +2617,7 @@
         <v>184</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>185</v>
+        <v>310</v>
       </c>
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
@@ -2615,7 +2675,7 @@
         <v>195</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>196</v>
+        <v>311</v>
       </c>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
@@ -2673,7 +2733,7 @@
         <v>207</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>208</v>
+        <v>312</v>
       </c>
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
@@ -2731,7 +2791,7 @@
         <v>218</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>219</v>
+        <v>313</v>
       </c>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
@@ -2789,7 +2849,7 @@
         <v>229</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>230</v>
+        <v>314</v>
       </c>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
@@ -2847,7 +2907,7 @@
         <v>240</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>241</v>
+        <v>315</v>
       </c>
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
@@ -4147,7 +4207,7 @@
       </c>
       <c r="F2" s="2" t="str">
         <f>Assessment!I2</f>
-        <v>Using data from contract management system, forecast monthly expense for all third-party contracts; Resilient logistics and planning</v>
+        <v/>
       </c>
       <c r="G2" s="2" t="str">
         <f t="shared" ref="G2:G21" si="0">IF(D2="Alta","Oleada 1",IF(D2="Media","Oleada 2","Oleada 3"))</f>
@@ -4182,7 +4242,7 @@
       </c>
       <c r="F3" s="2" t="str">
         <f>Assessment!I3</f>
-        <v>Resilient logistics and planning; Supplier assessment AI; Drafting contracts and SoWs</v>
+        <v/>
       </c>
       <c r="G3" s="2" t="str">
         <f t="shared" si="0"/>
@@ -4217,7 +4277,7 @@
       </c>
       <c r="F4" s="2" t="str">
         <f>Assessment!I4</f>
-        <v>Drafting contracts and SoWs; AI-powered RFP and knowledge assistant; Using data from contract management system forecast monthly expense</v>
+        <v/>
       </c>
       <c r="G4" s="2" t="str">
         <f t="shared" si="0"/>
@@ -4252,7 +4312,7 @@
       </c>
       <c r="F5" s="2" t="str">
         <f>Assessment!I5</f>
-        <v>Recommend most optimal payment timing; Proactive defect resolution recommendations; Guided adaptable workflows for master data record changes</v>
+        <v/>
       </c>
       <c r="G5" s="2" t="str">
         <f t="shared" si="0"/>
@@ -4287,7 +4347,7 @@
       </c>
       <c r="F6" s="2" t="str">
         <f>Assessment!I6</f>
-        <v>Read customer contracts and identify performance obligations; Identify &amp; proactively correct revenue leakage; AI assistant for vehicle buying and leasing</v>
+        <v/>
       </c>
       <c r="G6" s="2" t="str">
         <f t="shared" si="0"/>
@@ -4322,7 +4382,7 @@
       </c>
       <c r="F7" s="2" t="str">
         <f>Assessment!I7</f>
-        <v>Automated invoice error detection &amp; correction; Generate customized invoices for nonstandard customer orders</v>
+        <v/>
       </c>
       <c r="G7" s="2" t="str">
         <f t="shared" si="0"/>
@@ -4357,7 +4417,7 @@
       </c>
       <c r="F8" s="2" t="str">
         <f>Assessment!I8</f>
-        <v>Facilitate payment collection to identify collections gaps and automate outreach; Recommend optimal payment terms to improve DSO; Denial appeal letters</v>
+        <v/>
       </c>
       <c r="G8" s="2" t="str">
         <f t="shared" si="0"/>
@@ -4392,7 +4452,7 @@
       </c>
       <c r="F9" s="2" t="str">
         <f>Assessment!I9</f>
-        <v>AI agents for credit underwriting; Predicts late payments or defaults; Recommend optimal payment terms to improve DSO</v>
+        <v/>
       </c>
       <c r="G9" s="2" t="str">
         <f t="shared" si="0"/>
@@ -4427,7 +4487,7 @@
       </c>
       <c r="F10" s="2" t="str">
         <f>Assessment!I10</f>
-        <v>Identify expense classification errors; Generate metadata documentation; Guided adaptable workflows for master data record changes</v>
+        <v/>
       </c>
       <c r="G10" s="2" t="str">
         <f t="shared" si="0"/>
@@ -4462,7 +4522,7 @@
       </c>
       <c r="F11" s="2" t="str">
         <f>Assessment!I11</f>
-        <v>Identify inconsistencies in master data records; AI-powered archive access and extraction; Autonomous drone-based infrastructure inspection</v>
+        <v/>
       </c>
       <c r="G11" s="2" t="str">
         <f t="shared" si="0"/>
@@ -4497,7 +4557,7 @@
       </c>
       <c r="F12" s="2" t="str">
         <f>Assessment!I12</f>
-        <v>AI-driven predictive maintenance; Identify past data patterns to predict and improve future financial performance</v>
+        <v/>
       </c>
       <c r="G12" s="2" t="str">
         <f t="shared" si="0"/>
@@ -4532,7 +4592,7 @@
       </c>
       <c r="F13" s="2" t="str">
         <f>Assessment!I13</f>
-        <v>Project-level recommendations; AI-driven predictive maintenance; Autonomous drone-based infrastructure inspection</v>
+        <v/>
       </c>
       <c r="G13" s="2" t="str">
         <f t="shared" si="0"/>
@@ -4567,7 +4627,7 @@
       </c>
       <c r="F14" s="2" t="str">
         <f>Assessment!I14</f>
-        <v>Proactive defect resolution recommendations; Next-generation store operations; AI agents for service lifecycle management</v>
+        <v/>
       </c>
       <c r="G14" s="2" t="str">
         <f t="shared" si="0"/>
@@ -4602,7 +4662,7 @@
       </c>
       <c r="F15" s="2" t="str">
         <f>Assessment!I15</f>
-        <v>Guided adaptable workflows for master data record changes; Identify inconsistencies in master data records; Automate financial data across diverse sources</v>
+        <v/>
       </c>
       <c r="G15" s="2" t="str">
         <f t="shared" si="0"/>
@@ -4637,7 +4697,7 @@
       </c>
       <c r="F16" s="2" t="str">
         <f>Assessment!I16</f>
-        <v>Data access for all; Enterprise-wide data search and access; AI-powered archive access and extraction</v>
+        <v/>
       </c>
       <c r="G16" s="2" t="str">
         <f t="shared" si="0"/>
@@ -4672,7 +4732,7 @@
       </c>
       <c r="F17" s="2" t="str">
         <f>Assessment!I17</f>
-        <v>Proactive defect resolution recommendations; Autonomous field operations management; AI-driven permitting</v>
+        <v/>
       </c>
       <c r="G17" s="2" t="str">
         <f t="shared" si="0"/>
@@ -4707,7 +4767,7 @@
       </c>
       <c r="F18" s="2" t="str">
         <f>Assessment!I18</f>
-        <v>Drafting contracts and SoWs; Generate metadata documentation; AI-powered RFP and knowledge assistant</v>
+        <v/>
       </c>
       <c r="G18" s="2" t="str">
         <f t="shared" si="0"/>
@@ -4742,7 +4802,7 @@
       </c>
       <c r="F19" s="2" t="str">
         <f>Assessment!I19</f>
-        <v>Identify expense classification errors; Proactive defect resolution recommendations; Identify past data patterns to predict and improve future financial performance</v>
+        <v/>
       </c>
       <c r="G19" s="2" t="str">
         <f t="shared" si="0"/>
@@ -4777,7 +4837,7 @@
       </c>
       <c r="F20" s="2" t="str">
         <f>Assessment!I20</f>
-        <v>Read customer contracts and identify performance obligations; Identify &amp; proactively correct revenue leakage; Automated invoice error detection &amp; correction</v>
+        <v/>
       </c>
       <c r="G20" s="2" t="str">
         <f t="shared" si="0"/>
@@ -4812,7 +4872,7 @@
       </c>
       <c r="F21" s="2" t="str">
         <f>Assessment!I21</f>
-        <v>Identify past data patterns to predict and improve future financial performance; Generate executive level overview of company financial health; Project-level recommendations</v>
+        <v/>
       </c>
       <c r="G21" s="2" t="str">
         <f t="shared" si="0"/>
@@ -4872,7 +4932,7 @@
         <v>21</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>28</v>
+        <v>296</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>27</v>
@@ -4889,7 +4949,7 @@
         <v>32</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>39</v>
+        <v>297</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>38</v>
@@ -4906,7 +4966,7 @@
         <v>43</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>50</v>
+        <v>298</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>49</v>
@@ -4923,7 +4983,7 @@
         <v>54</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>61</v>
+        <v>299</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>60</v>
@@ -4940,7 +5000,7 @@
         <v>66</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>73</v>
+        <v>300</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>72</v>
@@ -4957,7 +5017,7 @@
         <v>77</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>84</v>
+        <v>301</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>83</v>
@@ -4974,7 +5034,7 @@
         <v>88</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>95</v>
+        <v>302</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>94</v>
@@ -4991,7 +5051,7 @@
         <v>99</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>106</v>
+        <v>303</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>105</v>
@@ -5008,7 +5068,7 @@
         <v>111</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>118</v>
+        <v>304</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>117</v>
@@ -5025,7 +5085,7 @@
         <v>122</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>129</v>
+        <v>305</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>128</v>
@@ -5042,7 +5102,7 @@
         <v>133</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>140</v>
+        <v>306</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>139</v>
@@ -5059,7 +5119,7 @@
         <v>144</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>151</v>
+        <v>307</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>150</v>
@@ -5076,7 +5136,7 @@
         <v>156</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>163</v>
+        <v>308</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>162</v>
@@ -5093,7 +5153,7 @@
         <v>167</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>174</v>
+        <v>309</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>173</v>
@@ -5110,7 +5170,7 @@
         <v>178</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>185</v>
+        <v>310</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>184</v>
@@ -5127,7 +5187,7 @@
         <v>189</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>196</v>
+        <v>311</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>195</v>
@@ -5144,7 +5204,7 @@
         <v>201</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>208</v>
+        <v>312</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>207</v>
@@ -5161,7 +5221,7 @@
         <v>212</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>219</v>
+        <v>313</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>218</v>
@@ -5178,7 +5238,7 @@
         <v>223</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>230</v>
+        <v>314</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>229</v>
@@ -5195,7 +5255,7 @@
         <v>234</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>241</v>
+        <v>315</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>240</v>

--- a/F3M_Transaccional_assessment_ready_AI.xlsx
+++ b/F3M_Transaccional_assessment_ready_AI.xlsx
@@ -132,7 +132,7 @@
     <t>Planificación integrada con negocio, contratos y presupuestos, con análisis de gasto y demanda recurrente.</t>
   </si>
   <si>
-    <t>Planificación predictiva de gasto y demanda de terceros basada en contratos, históricos y señales externas, con recomendaciones de sourcing y timing.</t>
+    <t>Planificación predictiva del gasto y la demanda de terceros a partir de contratos, histórico y señales externas, con recomendación de aprovisionamiento y de calendario.</t>
   </si>
   <si>
     <t>Previsión del gasto mensual de todos los contratos con terceros con datos del sistema de gestión de contratos; Logística y planificación resilientes</t>
@@ -168,7 +168,7 @@
     <t>Gestión integrada de desempeño, riesgos, cumplimiento y oportunidades de mejora por proveedor.</t>
   </si>
   <si>
-    <t>Motor IA de evaluación de proveedores, riesgo supply chain y recomendaciones de selección/negociación basadas en desempeño, riesgo y contexto externo.</t>
+    <t>Motor de IA para evaluar proveedores y el riesgo de la cadena de suministro, con recomendación de selección y de negociación según desempeño, riesgo y contexto externo.</t>
   </si>
   <si>
     <t>Logística y planificación resilientes; IA de evaluación de proveedores; Redacción de contratos y SoW</t>
@@ -204,7 +204,7 @@
     <t>Gestión contractual integrada con compras, legal, presupuesto y proveedores, con alertas y trazabilidad de cambios.</t>
   </si>
   <si>
-    <t>Asistente IA para generar RFPs, contratos y SoWs, extraer cláusulas, analizar riesgos y recomendar condiciones financieras/comerciales.</t>
+    <t>Asistente IA para generar RFP, contratos y SoW, extraer cláusulas, analizar riesgos y recomendar condiciones financieras/comerciales.</t>
   </si>
   <si>
     <t>Redacción de contratos y SoW; Asistente de RFP y de conocimiento impulsado por IA; Previsión del gasto mensual con datos del sistema de gestión de contratos</t>
@@ -240,7 +240,7 @@
     <t>Workflow integrado con catálogo, recepción, presupuesto, contrato y controles automáticos.</t>
   </si>
   <si>
-    <t>IA recomienda timing óptimo de pagos/compras, detecta excepciones operativas y prioriza aprobaciones según impacto en caja, contrato y riesgo.</t>
+    <t>IA recomienda momento óptimo de pagos/compras, detecta excepciones operativas y prioriza aprobaciones según impacto en caja, contrato y riesgo.</t>
   </si>
   <si>
     <t>Recomendación del momento óptimo de pago; Recomendaciones proactivas para la resolución de incidencias; Flujos guiados y adaptables para cambios en datos maestros</t>
@@ -279,7 +279,7 @@
     <t>Pedidos integrados con contratos, pricing, crédito, facturación y controles automáticos.</t>
   </si>
   <si>
-    <t>Asistente IA analiza contratos/pedidos, valida obligaciones y condiciones comerciales, y recomienda acciones para evitar errores, revenue leakage o disputas.</t>
+    <t>Asistente IA analiza contratos/pedidos, valida obligaciones y condiciones comerciales, y recomienda acciones para evitar errores, fuga de ingresos o disputas.</t>
   </si>
   <si>
     <t>Lectura de contratos de cliente e identificación de obligaciones de desempeño; Identificación y corrección proactiva de fugas de ingresos; Asistente de IA para la compra y el leasing de vehículos</t>
@@ -351,7 +351,7 @@
     <t>Cash application automatizada, segmentación de cartera, workflow de disputas y control de aging/DSO.</t>
   </si>
   <si>
-    <t>Asistente IA identifica gaps de cobro, automatiza outreach, recomienda payment terms para mejorar DSO y apoya recuperación de ingresos/disputas.</t>
+    <t>Un asistente de IA identifica las brechas de cobro, automatiza el contacto con el cliente, recomienda las condiciones de pago que mejoran el DSO y apoya la recuperación de ingresos y la gestión de disputas.</t>
   </si>
   <si>
     <t>Facilitación del cobro para identificar brechas de recobro y automatizar el contacto; Recomendación de condiciones de pago óptimas para mejorar el DSO; Cartas de recurso ante denegaciones</t>
@@ -387,7 +387,7 @@
     <t>Riesgo cliente integrado con pedidos, cobros, aging, límites y alertas de exposición.</t>
   </si>
   <si>
-    <t>Scoring dinámico IA de cliente y riesgo de cobro, con alertas tempranas, recomendaciones de bloqueo/liberación y condiciones comerciales.</t>
+    <t>Puntuación dinámica con IA del cliente y del riesgo de cobro, con alertas tempranas y recomendación de bloqueo o liberación y de condiciones comerciales.</t>
   </si>
   <si>
     <t>Agentes de IA para el análisis de riesgo crediticio; Predicción de retrasos en el pago o impagos; Recomendación de condiciones de pago óptimas para mejorar el DSO</t>
@@ -426,7 +426,7 @@
     <t>Proceso integrado con compras, proyectos, contabilidad y control presupuestario.</t>
   </si>
   <si>
-    <t>IA ayuda a clasificar gastos vs activos, detectar errores de codificación y generar metadata/documentación de activos.</t>
+    <t>IA ayuda a clasificar gastos vs activos, detectar errores de codificación y generar metadatos/documentación de activos.</t>
   </si>
   <si>
     <t>Identificación de errores de clasificación de gastos; Generación de documentación de metadatos; Flujos guiados y adaptables para cambios en datos maestros</t>
@@ -461,7 +461,7 @@
     <t>Trazabilidad integrada de altas, bajas, traslados, mantenimiento, ubicación y estado de activos.</t>
   </si>
   <si>
-    <t>IA/digital sensing permite detectar inconsistencias, anomalías de activos y generar alertas sobre activos críticos o no conciliados.</t>
+    <t>La IA, apoyada en sensorización digital, detecta inconsistencias y anomalías de activos y genera alertas sobre los activos críticos o no conciliados.</t>
   </si>
   <si>
     <t>Identificación de inconsistencias en los registros de datos maestros; Acceso y extracción documental impulsados por IA; Inspección autónoma de infraestructuras con drones</t>
@@ -497,7 +497,7 @@
     <t>Modelo integrado con reporting, planificación de activos, KPIs operativos y revisiones estructuradas.</t>
   </si>
   <si>
-    <t>Modelos IA detectan patrones de deterioro, anomalías de uso/coste y recomiendan revisión de vida útil, impairment o mantenimiento.</t>
+    <t>Modelos IA detectan patrones de deterioro, anomalías de uso/coste y recomiendan revisión de vida útil, deterioro o mantenimiento.</t>
   </si>
   <si>
     <t>Mantenimiento predictivo basado en IA; Identificación de patrones históricos para predecir y mejorar el rendimiento financiero futuro</t>
@@ -571,7 +571,7 @@
     <t>KPIs integrados, automatizados y conectados con procesos, productividad, coste y control.</t>
   </si>
   <si>
-    <t>IA genera alertas e insights operativos en tiempo real, detecta desviaciones y recomienda acciones de mejora.</t>
+    <t>La IA genera alertas y conclusiones operativas en tiempo real, detecta desviaciones y recomienda acciones de mejora.</t>
   </si>
   <si>
     <t>Recomendaciones proactivas para la resolución de incidencias; Operaciones de tienda de nueva generación; Agentes de IA para la gestión del ciclo de vida del servicio</t>
@@ -607,7 +607,7 @@
     <t>Capa integrada de datos operativos-financieros, controles automáticos y gestión de incidencias.</t>
   </si>
   <si>
-    <t>IA detecta inconsistencias en master data, automatiza datos de fuentes diversas y guía workflows de cambios de datos maestros.</t>
+    <t>IA detecta inconsistencias en datos maestros, automatiza datos de fuentes diversas y guía flujos de trabajo de cambios de datos maestros.</t>
   </si>
   <si>
     <t>Flujos guiados y adaptables para cambios en datos maestros; Identificación de inconsistencias en los registros de datos maestros; Automatización de datos financieros de fuentes diversas</t>
@@ -643,7 +643,7 @@
     <t>Reporting automatizado, con drill-down, alertas, comentarios y acceso por rol.</t>
   </si>
   <si>
-    <t>IA permite reporting operativo bajo demanda, búsqueda conversacional, extracción histórica y generación de resúmenes ejecutivos.</t>
+    <t>IA permite informes operativos bajo demanda, búsqueda conversacional, extracción histórica y generación de resúmenes ejecutivos.</t>
   </si>
   <si>
     <t>Acceso a datos para toda la organización; Búsqueda y acceso a datos en toda la compañía; Acceso y extracción documental impulsados por IA</t>
@@ -718,7 +718,7 @@
     <t>Alta integrada con business case, presupuesto, compras, tiempos, facturación y reporting.</t>
   </si>
   <si>
-    <t>IA asiste la creación de estructuras de proyecto, clasificación de costes, metadata y documentación a partir de contratos, SoWs y planes.</t>
+    <t>IA asiste la creación de estructuras de proyecto, clasificación de costes, metadatos y documentación a partir de contratos, SoW y planes.</t>
   </si>
   <si>
     <t>Redacción de contratos y SoW; Generación de documentación de metadatos; Asistente de RFP y de conocimiento impulsado por IA</t>
@@ -790,7 +790,7 @@
     <t>Integración entre contrato, avance, costes, facturación, ingresos y margen, con controles preventivos.</t>
   </si>
   <si>
-    <t>IA identifica obligaciones contractuales, genera alertas de hitos/facturación y detecta revenue leakage o riesgo de margen.</t>
+    <t>IA identifica obligaciones contractuales, genera alertas de hitos/facturación y detecta fuga de ingresos o riesgo de margen.</t>
   </si>
   <si>
     <t>Lectura de contratos de cliente e identificación de obligaciones de desempeño; Identificación y corrección proactiva de fugas de ingresos; Detección y corrección automatizada de errores en facturas</t>
@@ -826,7 +826,7 @@
     <t>Forecast integrado coste-ingreso-caja, revisión de margen, lecciones aprendidas y acciones de mejora.</t>
   </si>
   <si>
-    <t>IA predice performance futura del proyecto, genera escenarios, recomendaciones y resumen ejecutivo de salud financiera.</t>
+    <t>La IA predice el rendimiento futuro del proyecto y genera escenarios, recomendaciones y un resumen ejecutivo de su salud financiera.</t>
   </si>
   <si>
     <t>Identificación de patrones históricos para predecir y mejorar el rendimiento financiero futuro; Generación de una visión ejecutiva de la salud financiera de la compañía; Recomendaciones a nivel de proyecto</t>

--- a/F3M_Transaccional_assessment_ready_AI.xlsx
+++ b/F3M_Transaccional_assessment_ready_AI.xlsx
@@ -147,7 +147,7 @@
     <t>Plan de compras; category plans; forecast de gasto; contratos; presupuestos; análisis spend.</t>
   </si>
   <si>
-    <t>Implantar planificación de demanda de compras por categoría con forecast de gasto contractual y conexión con presupuesto.</t>
+    <t>Implantar planificación de demanda de compras por categoría con previsión de gasto contractual y conexión con presupuesto.</t>
   </si>
   <si>
     <t>1.2 Selección, evaluación y gestión de proveedores</t>
@@ -183,7 +183,7 @@
     <t>Scorecards proveedor; homologaciones; SLAs; incidencias; evaluación de riesgo; contratos.</t>
   </si>
   <si>
-    <t>Crear modelo de supplier intelligence con indicadores de desempeño, riesgo, compliance y recomendaciones de sourcing.</t>
+    <t>Crear modelo de inteligencia de proveedores con indicadores de desempeño, riesgo, cumplimiento y recomendaciones de aprovisionamiento.</t>
   </si>
   <si>
     <t>1.3 Gestión contractual, RFPs y SoWs</t>
@@ -255,7 +255,7 @@
     <t>PR/PO; workflow; recepción; aprobaciones; excepciones; controles presupuestarios.</t>
   </si>
   <si>
-    <t>Digitalizar workflow PR/PO/recepción con controles automáticos, excepciones y recomendaciones de aprobación/pago.</t>
+    <t>Digitalizar el flujo de solicitud, pedido y recepción con controles automáticos, excepciones y recomendaciones de aprobación y pago.</t>
   </si>
   <si>
     <t>Order-to-Cash</t>
@@ -294,7 +294,7 @@
     <t>Pedidos; contratos; pricing; aprobaciones; incidencias; ajustes comerciales; revenue leakage.</t>
   </si>
   <si>
-    <t>Crear controles automáticos de pedido/contrato/precio con detección de condiciones atípicas y revenue leakage.</t>
+    <t>Crear controles automáticos de pedido/contrato/precio con detección de condiciones atípicas y fugas de ingresos.</t>
   </si>
   <si>
     <t>2.2 Facturación y emisión de documentos</t>
@@ -366,7 +366,7 @@
     <t>Aging; DSO; cash application; disputas; recordatorios; comunicaciones; write-offs.</t>
   </si>
   <si>
-    <t>Desplegar asistente de cobranzas/intelligent collections con priorización, outreach automatizado y recomendaciones de términos.</t>
+    <t>Desplegar asistente inteligente de gestión de cobros con priorización, contacto automatizado con clientes y recomendaciones de condiciones.</t>
   </si>
   <si>
     <t>2.4 Crédito, riesgo cliente y control de exposición</t>
@@ -440,7 +440,7 @@
     <t>Política CAPEX; altas de activos; facturas; órdenes de compra; controles; maestro de activos.</t>
   </si>
   <si>
-    <t>Implantar clasificación asistida CAPEX/OPEX y workflow de alta de activos con controles de soporte documental.</t>
+    <t>Implantar clasificación asistida CAPEX/OPEX y flujo de alta de activos con controles de soporte documental.</t>
   </si>
   <si>
     <t>3.2 Inventario, localización y trazabilidad de activos</t>
@@ -476,7 +476,7 @@
     <t>Maestro de activos; inventario físico; conciliaciones; incidencias; ubicación; bajas/traslados.</t>
   </si>
   <si>
-    <t>Crear modelo de asset intelligence con calidad de master data, inventario, conciliación y trazabilidad de ciclo de vida.</t>
+    <t>Crear modelo de inteligencia de activos con calidad de datos maestros, inventario, conciliación y trazabilidad del ciclo de vida.</t>
   </si>
   <si>
     <t>3.3 Depreciación, impairments y valoración</t>
@@ -547,7 +547,7 @@
     <t>Bajas; autorizaciones; CAPEX; business cases; desviaciones; resultados de disposición.</t>
   </si>
   <si>
-    <t>Implantar control de CAPEX/asset lifecycle con analítica de coste evitado, riesgo y priorización de inversión/desinversión.</t>
+    <t>Implantar control del CAPEX y del ciclo de vida de los activos con analítica de coste evitado, riesgo y priorización de inversión y desinversión.</t>
   </si>
   <si>
     <t>Informes operativos</t>
@@ -586,7 +586,7 @@
     <t>Catálogo de KPIs; dashboards; fuentes; definiciones; owners; actas de revisión.</t>
   </si>
   <si>
-    <t>Rediseñar reporting operativo-financiero con KPIs homogéneos, alertas y explicación automática de desviaciones.</t>
+    <t>Rediseñar los informes operativo-financieros con KPIs homogéneos, alertas y explicación automática de desviaciones.</t>
   </si>
   <si>
     <t>4.2 Calidad, integración y gobierno de datos operativos</t>
@@ -622,7 +622,7 @@
     <t>Modelo de datos; fuentes; reglas de calidad; incidencias; maestro; logs de carga.</t>
   </si>
   <si>
-    <t>Implantar gobierno de datos operativos-financieros con controles de calidad, master data management y workflow de remediación.</t>
+    <t>Implantar gobierno de datos operativos-financieros con controles de calidad, gestión de datos maestros y flujo de corrección.</t>
   </si>
   <si>
     <t>4.3 Automatización del reporting operativo</t>
@@ -658,7 +658,7 @@
     <t>Dashboards; reportes; logs de actualización; usuarios; permisos; plantillas.</t>
   </si>
   <si>
-    <t>Construir reporting operativo autoservicio con capa conversacional, extracción de datos y generación automática de insights.</t>
+    <t>Construir informes operativos en autoservicio con capa conversacional, extracción de datos y generación automática de conclusiones.</t>
   </si>
   <si>
     <t>4.4 Rutinas de gestión, incidencias y mejora continua</t>
@@ -694,7 +694,7 @@
     <t>Trackers de acciones; incidencias; actas; KPIs; planes de mejora; análisis causa-raíz.</t>
   </si>
   <si>
-    <t>Implantar workflow de gestión de incidencias con priorización IA, root cause y seguimiento de beneficios.</t>
+    <t>Implantar flujo de gestión de incidencias con priorización por IA, causa raíz y seguimiento de beneficios.</t>
   </si>
   <si>
     <t>Contabilidad de proyectos</t>
@@ -733,7 +733,7 @@
     <t>Alta proyecto; WBS; presupuesto; contrato; SoW; maestro de proyectos; aprobaciones.</t>
   </si>
   <si>
-    <t>Crear workflow de alta de proyectos con estructura estándar, metadata automática y conexión con contrato/presupuesto.</t>
+    <t>Crear flujo de alta de proyectos con estructura estándar, metadatos automáticos y conexión con contrato y presupuesto.</t>
   </si>
   <si>
     <t>5.2 Registro, imputación y control de costes</t>
@@ -805,7 +805,7 @@
     <t>Contrato; hitos; facturas; ingresos; margen; avance; notas de crédito; revenue recognition.</t>
   </si>
   <si>
-    <t>Crear control IA de contrato-hito-factura-ingreso-margen para proyectos, con alertas de leakage y desviaciones.</t>
+    <t>Crear control con IA de contrato-hito-factura-ingreso-margen para proyectos, con alertas de fugas y desviaciones.</t>
   </si>
   <si>
     <t>5.4 Forecast, cierre y análisis del proyecto</t>
@@ -841,7 +841,7 @@
     <t>Forecast; margen; cash flow proyecto; cierre; post-mortem; acciones de mejora; reporting ejecutivo.</t>
   </si>
   <si>
-    <t>Implantar forecast predictivo de proyectos con escenarios, alertas de margen/caja y recomendaciones de acción.</t>
+    <t>Implantar previsión predictiva de proyectos con escenarios, alertas de margen y caja y recomendaciones de acción.</t>
   </si>
   <si>
     <t>Score global dominio</t>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="E2" s="2" t="str">
         <f>Assessment!S2</f>
-        <v>Implantar planificación de demanda de compras por categoría con forecast de gasto contractual y conexión con presupuesto.</v>
+        <v>Implantar planificación de demanda de compras por categoría con previsión de gasto contractual y conexión con presupuesto.</v>
       </c>
       <c r="F2" s="2" t="str">
         <f>Assessment!I2</f>
@@ -4238,7 +4238,7 @@
       </c>
       <c r="E3" s="2" t="str">
         <f>Assessment!S3</f>
-        <v>Crear modelo de supplier intelligence con indicadores de desempeño, riesgo, compliance y recomendaciones de sourcing.</v>
+        <v>Crear modelo de inteligencia de proveedores con indicadores de desempeño, riesgo, cumplimiento y recomendaciones de aprovisionamiento.</v>
       </c>
       <c r="F3" s="2" t="str">
         <f>Assessment!I3</f>
@@ -4308,7 +4308,7 @@
       </c>
       <c r="E5" s="2" t="str">
         <f>Assessment!S5</f>
-        <v>Digitalizar workflow PR/PO/recepción con controles automáticos, excepciones y recomendaciones de aprobación/pago.</v>
+        <v>Digitalizar el flujo de solicitud, pedido y recepción con controles automáticos, excepciones y recomendaciones de aprobación y pago.</v>
       </c>
       <c r="F5" s="2" t="str">
         <f>Assessment!I5</f>
@@ -4343,7 +4343,7 @@
       </c>
       <c r="E6" s="2" t="str">
         <f>Assessment!S6</f>
-        <v>Crear controles automáticos de pedido/contrato/precio con detección de condiciones atípicas y revenue leakage.</v>
+        <v>Crear controles automáticos de pedido/contrato/precio con detección de condiciones atípicas y fugas de ingresos.</v>
       </c>
       <c r="F6" s="2" t="str">
         <f>Assessment!I6</f>
@@ -4413,7 +4413,7 @@
       </c>
       <c r="E8" s="2" t="str">
         <f>Assessment!S8</f>
-        <v>Desplegar asistente de cobranzas/intelligent collections con priorización, outreach automatizado y recomendaciones de términos.</v>
+        <v>Desplegar asistente inteligente de gestión de cobros con priorización, contacto automatizado con clientes y recomendaciones de condiciones.</v>
       </c>
       <c r="F8" s="2" t="str">
         <f>Assessment!I8</f>
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E10" s="2" t="str">
         <f>Assessment!S10</f>
-        <v>Implantar clasificación asistida CAPEX/OPEX y workflow de alta de activos con controles de soporte documental.</v>
+        <v>Implantar clasificación asistida CAPEX/OPEX y flujo de alta de activos con controles de soporte documental.</v>
       </c>
       <c r="F10" s="2" t="str">
         <f>Assessment!I10</f>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="E11" s="2" t="str">
         <f>Assessment!S11</f>
-        <v>Crear modelo de asset intelligence con calidad de master data, inventario, conciliación y trazabilidad de ciclo de vida.</v>
+        <v>Crear modelo de inteligencia de activos con calidad de datos maestros, inventario, conciliación y trazabilidad del ciclo de vida.</v>
       </c>
       <c r="F11" s="2" t="str">
         <f>Assessment!I11</f>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="E13" s="2" t="str">
         <f>Assessment!S13</f>
-        <v>Implantar control de CAPEX/asset lifecycle con analítica de coste evitado, riesgo y priorización de inversión/desinversión.</v>
+        <v>Implantar control del CAPEX y del ciclo de vida de los activos con analítica de coste evitado, riesgo y priorización de inversión y desinversión.</v>
       </c>
       <c r="F13" s="2" t="str">
         <f>Assessment!I13</f>
@@ -4623,7 +4623,7 @@
       </c>
       <c r="E14" s="2" t="str">
         <f>Assessment!S14</f>
-        <v>Rediseñar reporting operativo-financiero con KPIs homogéneos, alertas y explicación automática de desviaciones.</v>
+        <v>Rediseñar los informes operativo-financieros con KPIs homogéneos, alertas y explicación automática de desviaciones.</v>
       </c>
       <c r="F14" s="2" t="str">
         <f>Assessment!I14</f>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="E15" s="2" t="str">
         <f>Assessment!S15</f>
-        <v>Implantar gobierno de datos operativos-financieros con controles de calidad, master data management y workflow de remediación.</v>
+        <v>Implantar gobierno de datos operativos-financieros con controles de calidad, gestión de datos maestros y flujo de corrección.</v>
       </c>
       <c r="F15" s="2" t="str">
         <f>Assessment!I15</f>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="E16" s="2" t="str">
         <f>Assessment!S16</f>
-        <v>Construir reporting operativo autoservicio con capa conversacional, extracción de datos y generación automática de insights.</v>
+        <v>Construir informes operativos en autoservicio con capa conversacional, extracción de datos y generación automática de conclusiones.</v>
       </c>
       <c r="F16" s="2" t="str">
         <f>Assessment!I16</f>
@@ -4763,7 +4763,7 @@
       </c>
       <c r="E18" s="2" t="str">
         <f>Assessment!S18</f>
-        <v>Crear workflow de alta de proyectos con estructura estándar, metadata automática y conexión con contrato/presupuesto.</v>
+        <v>Crear flujo de alta de proyectos con estructura estándar, metadatos automáticos y conexión con contrato y presupuesto.</v>
       </c>
       <c r="F18" s="2" t="str">
         <f>Assessment!I18</f>
@@ -4868,7 +4868,7 @@
       </c>
       <c r="E21" s="2" t="str">
         <f>Assessment!S21</f>
-        <v>Implantar forecast predictivo de proyectos con escenarios, alertas de margen/caja y recomendaciones de acción.</v>
+        <v>Implantar previsión predictiva de proyectos con escenarios, alertas de margen y caja y recomendaciones de acción.</v>
       </c>
       <c r="F21" s="2" t="str">
         <f>Assessment!I21</f>
